--- a/VERTEX_Instructores_Modelo.xlsx
+++ b/VERTEX_Instructores_Modelo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agust\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EE681D1-3230-4484-943A-F38A0E2CC779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10D75A6F-87C2-4ECB-ADF8-79537134419F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -146,7 +146,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -169,11 +169,135 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD1D5DB"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD1D5DB"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -187,12 +311,51 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -521,24 +684,34 @@
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
+      <c r="I1" s="7"/>
     </row>
     <row r="2" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-    </row>
-    <row r="3" spans="1:9" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="10"/>
+    </row>
+    <row r="3" spans="1:9" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="11"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="13"/>
+    </row>
     <row r="4" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="14" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -562,12 +735,12 @@
       <c r="H4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="15" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="16" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -591,12 +764,12 @@
       <c r="H5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="17" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4"/>
+      <c r="A6" s="18"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -604,10 +777,10 @@
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
+      <c r="I6" s="19"/>
     </row>
     <row r="7" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
+      <c r="A7" s="20"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
@@ -615,10 +788,10 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+      <c r="I7" s="21"/>
     </row>
     <row r="8" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
+      <c r="A8" s="18"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -626,10 +799,10 @@
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
+      <c r="I8" s="19"/>
     </row>
     <row r="9" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
+      <c r="A9" s="20"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
@@ -637,10 +810,10 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+      <c r="I9" s="21"/>
     </row>
     <row r="10" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
+      <c r="A10" s="18"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -648,10 +821,10 @@
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
+      <c r="I10" s="19"/>
     </row>
     <row r="11" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3"/>
+      <c r="A11" s="20"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
@@ -659,10 +832,10 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
+      <c r="I11" s="21"/>
     </row>
     <row r="12" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
+      <c r="A12" s="18"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
@@ -670,10 +843,10 @@
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
+      <c r="I12" s="19"/>
     </row>
     <row r="13" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3"/>
+      <c r="A13" s="20"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
@@ -681,10 +854,10 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+      <c r="I13" s="21"/>
     </row>
     <row r="14" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
+      <c r="A14" s="18"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
@@ -692,10 +865,10 @@
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
+      <c r="I14" s="19"/>
     </row>
     <row r="15" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3"/>
+      <c r="A15" s="20"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
@@ -703,10 +876,10 @@
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
+      <c r="I15" s="21"/>
     </row>
     <row r="16" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="4"/>
+      <c r="A16" s="18"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
@@ -714,10 +887,10 @@
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
+      <c r="I16" s="19"/>
     </row>
     <row r="17" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3"/>
+      <c r="A17" s="20"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
@@ -725,10 +898,10 @@
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
+      <c r="I17" s="21"/>
     </row>
     <row r="18" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="4"/>
+      <c r="A18" s="18"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
@@ -736,10 +909,10 @@
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
+      <c r="I18" s="19"/>
     </row>
     <row r="19" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="3"/>
+      <c r="A19" s="20"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -747,10 +920,10 @@
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
+      <c r="I19" s="21"/>
     </row>
     <row r="20" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="4"/>
+      <c r="A20" s="18"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
@@ -758,10 +931,10 @@
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
+      <c r="I20" s="19"/>
     </row>
     <row r="21" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="3"/>
+      <c r="A21" s="20"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
@@ -769,10 +942,10 @@
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
+      <c r="I21" s="21"/>
     </row>
     <row r="22" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="4"/>
+      <c r="A22" s="18"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
@@ -780,10 +953,10 @@
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
+      <c r="I22" s="19"/>
     </row>
     <row r="23" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="3"/>
+      <c r="A23" s="20"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
@@ -791,10 +964,10 @@
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
+      <c r="I23" s="21"/>
     </row>
     <row r="24" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="4"/>
+      <c r="A24" s="18"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
@@ -802,10 +975,10 @@
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
+      <c r="I24" s="19"/>
     </row>
     <row r="25" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="3"/>
+      <c r="A25" s="20"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -813,10 +986,10 @@
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
+      <c r="I25" s="21"/>
     </row>
     <row r="26" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="4"/>
+      <c r="A26" s="18"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
@@ -824,10 +997,10 @@
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
+      <c r="I26" s="19"/>
     </row>
     <row r="27" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="3"/>
+      <c r="A27" s="20"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
@@ -835,10 +1008,10 @@
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
+      <c r="I27" s="21"/>
     </row>
     <row r="28" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="4"/>
+      <c r="A28" s="18"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
@@ -846,10 +1019,10 @@
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
+      <c r="I28" s="19"/>
     </row>
     <row r="29" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="3"/>
+      <c r="A29" s="20"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
@@ -857,10 +1030,10 @@
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
+      <c r="I29" s="21"/>
     </row>
     <row r="30" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="4"/>
+      <c r="A30" s="18"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
@@ -868,10 +1041,10 @@
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
+      <c r="I30" s="19"/>
     </row>
     <row r="31" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="3"/>
+      <c r="A31" s="20"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
@@ -879,10 +1052,10 @@
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
+      <c r="I31" s="21"/>
     </row>
     <row r="32" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="4"/>
+      <c r="A32" s="18"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
@@ -890,10 +1063,10 @@
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
+      <c r="I32" s="19"/>
     </row>
     <row r="33" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="3"/>
+      <c r="A33" s="20"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
@@ -901,10 +1074,10 @@
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
+      <c r="I33" s="21"/>
     </row>
     <row r="34" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="4"/>
+      <c r="A34" s="18"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
@@ -912,10 +1085,10 @@
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
+      <c r="I34" s="19"/>
     </row>
     <row r="35" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="3"/>
+      <c r="A35" s="20"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
@@ -923,10 +1096,10 @@
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
+      <c r="I35" s="21"/>
     </row>
     <row r="36" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="4"/>
+      <c r="A36" s="18"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
@@ -934,10 +1107,10 @@
       <c r="F36" s="4"/>
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
+      <c r="I36" s="19"/>
     </row>
     <row r="37" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="3"/>
+      <c r="A37" s="20"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
@@ -945,10 +1118,10 @@
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
+      <c r="I37" s="21"/>
     </row>
     <row r="38" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="4"/>
+      <c r="A38" s="18"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
@@ -956,10 +1129,10 @@
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
+      <c r="I38" s="19"/>
     </row>
     <row r="39" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="3"/>
+      <c r="A39" s="20"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
@@ -967,10 +1140,10 @@
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
+      <c r="I39" s="21"/>
     </row>
     <row r="40" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="4"/>
+      <c r="A40" s="18"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
@@ -978,10 +1151,10 @@
       <c r="F40" s="4"/>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
+      <c r="I40" s="19"/>
     </row>
     <row r="41" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="3"/>
+      <c r="A41" s="20"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
@@ -989,10 +1162,10 @@
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
+      <c r="I41" s="21"/>
     </row>
     <row r="42" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="4"/>
+      <c r="A42" s="18"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
@@ -1000,10 +1173,10 @@
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
-      <c r="I42" s="4"/>
+      <c r="I42" s="19"/>
     </row>
     <row r="43" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="3"/>
+      <c r="A43" s="20"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
@@ -1011,10 +1184,10 @@
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
-      <c r="I43" s="3"/>
+      <c r="I43" s="21"/>
     </row>
     <row r="44" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="4"/>
+      <c r="A44" s="18"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
@@ -1022,10 +1195,10 @@
       <c r="F44" s="4"/>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
-      <c r="I44" s="4"/>
+      <c r="I44" s="19"/>
     </row>
     <row r="45" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="3"/>
+      <c r="A45" s="20"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
@@ -1033,10 +1206,10 @@
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
-      <c r="I45" s="3"/>
+      <c r="I45" s="21"/>
     </row>
     <row r="46" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="4"/>
+      <c r="A46" s="18"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
@@ -1044,10 +1217,10 @@
       <c r="F46" s="4"/>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
-      <c r="I46" s="4"/>
+      <c r="I46" s="19"/>
     </row>
     <row r="47" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="3"/>
+      <c r="A47" s="20"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
@@ -1055,10 +1228,10 @@
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
-      <c r="I47" s="3"/>
+      <c r="I47" s="21"/>
     </row>
     <row r="48" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="4"/>
+      <c r="A48" s="18"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
@@ -1066,10 +1239,10 @@
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
-      <c r="I48" s="4"/>
+      <c r="I48" s="19"/>
     </row>
     <row r="49" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="3"/>
+      <c r="A49" s="20"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
@@ -1077,10 +1250,10 @@
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
-      <c r="I49" s="3"/>
+      <c r="I49" s="21"/>
     </row>
     <row r="50" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="4"/>
+      <c r="A50" s="18"/>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
@@ -1088,10 +1261,10 @@
       <c r="F50" s="4"/>
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
-      <c r="I50" s="4"/>
+      <c r="I50" s="19"/>
     </row>
     <row r="51" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="3"/>
+      <c r="A51" s="20"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
@@ -1099,10 +1272,10 @@
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
-      <c r="I51" s="3"/>
+      <c r="I51" s="21"/>
     </row>
     <row r="52" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="4"/>
+      <c r="A52" s="18"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
@@ -1110,10 +1283,10 @@
       <c r="F52" s="4"/>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
-      <c r="I52" s="4"/>
+      <c r="I52" s="19"/>
     </row>
     <row r="53" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="3"/>
+      <c r="A53" s="20"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
@@ -1121,10 +1294,10 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
-      <c r="I53" s="3"/>
+      <c r="I53" s="21"/>
     </row>
     <row r="54" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="4"/>
+      <c r="A54" s="18"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
@@ -1132,10 +1305,10 @@
       <c r="F54" s="4"/>
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
-      <c r="I54" s="4"/>
+      <c r="I54" s="19"/>
     </row>
     <row r="55" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="3"/>
+      <c r="A55" s="20"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
@@ -1143,18 +1316,18 @@
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
-      <c r="I55" s="3"/>
+      <c r="I55" s="21"/>
     </row>
     <row r="56" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="4"/>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="4"/>
-      <c r="G56" s="4"/>
-      <c r="H56" s="4"/>
-      <c r="I56" s="4"/>
+      <c r="A56" s="22"/>
+      <c r="B56" s="23"/>
+      <c r="C56" s="23"/>
+      <c r="D56" s="23"/>
+      <c r="E56" s="23"/>
+      <c r="F56" s="23"/>
+      <c r="G56" s="23"/>
+      <c r="H56" s="23"/>
+      <c r="I56" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/VERTEX_Instructores_Modelo.xlsx
+++ b/VERTEX_Instructores_Modelo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agust\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10D75A6F-87C2-4ECB-ADF8-79537134419F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D62F9CB6-51C4-41A9-BBEC-CCD9980CA5CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -73,13 +73,13 @@
     <t>Esqui / Snowboard / Esqui Adaptado (separar con coma)</t>
   </si>
   <si>
-    <t>Inglés, Portugués, Francés, Alemán, Italiano</t>
-  </si>
-  <si>
     <t>SI o NO</t>
   </si>
   <si>
     <t>DD/MM/AAAA</t>
+  </si>
+  <si>
+    <t>Inglés, Portugués, Francés, Alemán, Italiano (separar con coma)</t>
   </si>
 </sst>
 </file>
@@ -146,7 +146,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -169,135 +169,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD1D5DB"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD1D5DB"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD1D5DB"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD1D5DB"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD1D5DB"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD1D5DB"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD1D5DB"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD1D5DB"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD1D5DB"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD1D5DB"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD1D5DB"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD1D5DB"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD1D5DB"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -311,51 +187,18 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -662,56 +505,46 @@
   <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.5703125" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="30.85546875" customWidth="1"/>
+    <col min="6" max="6" width="35.140625" customWidth="1"/>
+    <col min="7" max="7" width="32.28515625" customWidth="1"/>
     <col min="8" max="8" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="7"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
     </row>
     <row r="2" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="10"/>
-    </row>
-    <row r="3" spans="1:9" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="13"/>
-    </row>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+    </row>
+    <row r="3" spans="1:9" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -735,12 +568,12 @@
       <c r="H4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="15" t="s">
+      <c r="I4" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -759,575 +592,575 @@
         <v>16</v>
       </c>
       <c r="G5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="17" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="6" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="18"/>
+      <c r="A6" s="4"/>
       <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
+      <c r="C6" s="6"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
-      <c r="I6" s="19"/>
+      <c r="I6" s="4"/>
     </row>
     <row r="7" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="20"/>
+      <c r="A7" s="3"/>
       <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
+      <c r="C7" s="5"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
-      <c r="I7" s="21"/>
+      <c r="I7" s="3"/>
     </row>
     <row r="8" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="18"/>
+      <c r="A8" s="4"/>
       <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
+      <c r="C8" s="6"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
-      <c r="I8" s="19"/>
+      <c r="I8" s="4"/>
     </row>
     <row r="9" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="20"/>
+      <c r="A9" s="3"/>
       <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
+      <c r="C9" s="5"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
-      <c r="I9" s="21"/>
+      <c r="I9" s="3"/>
     </row>
     <row r="10" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="18"/>
+      <c r="A10" s="4"/>
       <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
+      <c r="C10" s="6"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
-      <c r="I10" s="19"/>
+      <c r="I10" s="4"/>
     </row>
     <row r="11" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="20"/>
+      <c r="A11" s="3"/>
       <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
+      <c r="C11" s="5"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
-      <c r="I11" s="21"/>
+      <c r="I11" s="3"/>
     </row>
     <row r="12" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="18"/>
+      <c r="A12" s="4"/>
       <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
+      <c r="C12" s="6"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
-      <c r="I12" s="19"/>
+      <c r="I12" s="4"/>
     </row>
     <row r="13" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="20"/>
+      <c r="A13" s="3"/>
       <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
+      <c r="C13" s="5"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
-      <c r="I13" s="21"/>
+      <c r="I13" s="3"/>
     </row>
     <row r="14" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="18"/>
+      <c r="A14" s="4"/>
       <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
+      <c r="C14" s="6"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
-      <c r="I14" s="19"/>
+      <c r="I14" s="4"/>
     </row>
     <row r="15" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="20"/>
+      <c r="A15" s="3"/>
       <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
+      <c r="C15" s="5"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
-      <c r="I15" s="21"/>
+      <c r="I15" s="3"/>
     </row>
     <row r="16" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="18"/>
+      <c r="A16" s="4"/>
       <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
+      <c r="C16" s="6"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
-      <c r="I16" s="19"/>
+      <c r="I16" s="4"/>
     </row>
     <row r="17" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="20"/>
+      <c r="A17" s="3"/>
       <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
+      <c r="C17" s="5"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
-      <c r="I17" s="21"/>
+      <c r="I17" s="3"/>
     </row>
     <row r="18" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="18"/>
+      <c r="A18" s="4"/>
       <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
+      <c r="C18" s="6"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
-      <c r="I18" s="19"/>
+      <c r="I18" s="4"/>
     </row>
     <row r="19" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="20"/>
+      <c r="A19" s="3"/>
       <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
+      <c r="C19" s="5"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
-      <c r="I19" s="21"/>
+      <c r="I19" s="3"/>
     </row>
     <row r="20" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="18"/>
+      <c r="A20" s="4"/>
       <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
+      <c r="C20" s="6"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
-      <c r="I20" s="19"/>
+      <c r="I20" s="4"/>
     </row>
     <row r="21" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="20"/>
+      <c r="A21" s="3"/>
       <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
+      <c r="C21" s="5"/>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
-      <c r="I21" s="21"/>
+      <c r="I21" s="3"/>
     </row>
     <row r="22" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="18"/>
+      <c r="A22" s="4"/>
       <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
+      <c r="C22" s="6"/>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
-      <c r="I22" s="19"/>
+      <c r="I22" s="4"/>
     </row>
     <row r="23" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="20"/>
+      <c r="A23" s="3"/>
       <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
+      <c r="C23" s="5"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
-      <c r="I23" s="21"/>
+      <c r="I23" s="3"/>
     </row>
     <row r="24" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="18"/>
+      <c r="A24" s="4"/>
       <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
+      <c r="C24" s="6"/>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
-      <c r="I24" s="19"/>
+      <c r="I24" s="4"/>
     </row>
     <row r="25" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="20"/>
+      <c r="A25" s="3"/>
       <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
+      <c r="C25" s="5"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
-      <c r="I25" s="21"/>
+      <c r="I25" s="3"/>
     </row>
     <row r="26" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="18"/>
+      <c r="A26" s="4"/>
       <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
+      <c r="C26" s="6"/>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
-      <c r="I26" s="19"/>
+      <c r="I26" s="4"/>
     </row>
     <row r="27" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="20"/>
+      <c r="A27" s="3"/>
       <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
+      <c r="C27" s="5"/>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
-      <c r="I27" s="21"/>
+      <c r="I27" s="3"/>
     </row>
     <row r="28" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="18"/>
+      <c r="A28" s="4"/>
       <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
+      <c r="C28" s="6"/>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
-      <c r="I28" s="19"/>
+      <c r="I28" s="4"/>
     </row>
     <row r="29" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="20"/>
+      <c r="A29" s="3"/>
       <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
+      <c r="C29" s="5"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
-      <c r="I29" s="21"/>
+      <c r="I29" s="3"/>
     </row>
     <row r="30" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="18"/>
+      <c r="A30" s="4"/>
       <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
+      <c r="C30" s="6"/>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
-      <c r="I30" s="19"/>
+      <c r="I30" s="4"/>
     </row>
     <row r="31" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="20"/>
+      <c r="A31" s="3"/>
       <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
+      <c r="C31" s="5"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
-      <c r="I31" s="21"/>
+      <c r="I31" s="3"/>
     </row>
     <row r="32" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="18"/>
+      <c r="A32" s="4"/>
       <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
+      <c r="C32" s="6"/>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
-      <c r="I32" s="19"/>
+      <c r="I32" s="4"/>
     </row>
     <row r="33" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="20"/>
+      <c r="A33" s="3"/>
       <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
+      <c r="C33" s="5"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
-      <c r="I33" s="21"/>
+      <c r="I33" s="3"/>
     </row>
     <row r="34" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="18"/>
+      <c r="A34" s="4"/>
       <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
+      <c r="C34" s="6"/>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
-      <c r="I34" s="19"/>
+      <c r="I34" s="4"/>
     </row>
     <row r="35" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="20"/>
+      <c r="A35" s="3"/>
       <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
+      <c r="C35" s="5"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
-      <c r="I35" s="21"/>
+      <c r="I35" s="3"/>
     </row>
     <row r="36" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="18"/>
+      <c r="A36" s="4"/>
       <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
+      <c r="C36" s="6"/>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
-      <c r="I36" s="19"/>
+      <c r="I36" s="4"/>
     </row>
     <row r="37" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="20"/>
+      <c r="A37" s="3"/>
       <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
+      <c r="C37" s="5"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
-      <c r="I37" s="21"/>
+      <c r="I37" s="3"/>
     </row>
     <row r="38" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="18"/>
+      <c r="A38" s="4"/>
       <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
+      <c r="C38" s="6"/>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
-      <c r="I38" s="19"/>
+      <c r="I38" s="4"/>
     </row>
     <row r="39" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="20"/>
+      <c r="A39" s="3"/>
       <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
+      <c r="C39" s="5"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
-      <c r="I39" s="21"/>
+      <c r="I39" s="3"/>
     </row>
     <row r="40" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="18"/>
+      <c r="A40" s="4"/>
       <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
+      <c r="C40" s="6"/>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
-      <c r="I40" s="19"/>
+      <c r="I40" s="4"/>
     </row>
     <row r="41" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="20"/>
+      <c r="A41" s="3"/>
       <c r="B41" s="3"/>
-      <c r="C41" s="3"/>
+      <c r="C41" s="5"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
-      <c r="I41" s="21"/>
+      <c r="I41" s="3"/>
     </row>
     <row r="42" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="18"/>
+      <c r="A42" s="4"/>
       <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
+      <c r="C42" s="6"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
-      <c r="I42" s="19"/>
+      <c r="I42" s="4"/>
     </row>
     <row r="43" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="20"/>
+      <c r="A43" s="3"/>
       <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
+      <c r="C43" s="5"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
-      <c r="I43" s="21"/>
+      <c r="I43" s="3"/>
     </row>
     <row r="44" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="18"/>
+      <c r="A44" s="4"/>
       <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
+      <c r="C44" s="6"/>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
-      <c r="I44" s="19"/>
+      <c r="I44" s="4"/>
     </row>
     <row r="45" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="20"/>
+      <c r="A45" s="3"/>
       <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
+      <c r="C45" s="5"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
-      <c r="I45" s="21"/>
+      <c r="I45" s="3"/>
     </row>
     <row r="46" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="18"/>
+      <c r="A46" s="4"/>
       <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
+      <c r="C46" s="6"/>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
-      <c r="I46" s="19"/>
+      <c r="I46" s="4"/>
     </row>
     <row r="47" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="20"/>
+      <c r="A47" s="3"/>
       <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
+      <c r="C47" s="5"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
-      <c r="I47" s="21"/>
+      <c r="I47" s="3"/>
     </row>
     <row r="48" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="18"/>
+      <c r="A48" s="4"/>
       <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
+      <c r="C48" s="6"/>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
-      <c r="I48" s="19"/>
+      <c r="I48" s="4"/>
     </row>
     <row r="49" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="20"/>
+      <c r="A49" s="3"/>
       <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
+      <c r="C49" s="5"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
-      <c r="I49" s="21"/>
+      <c r="I49" s="3"/>
     </row>
     <row r="50" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="18"/>
+      <c r="A50" s="4"/>
       <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
+      <c r="C50" s="6"/>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
-      <c r="I50" s="19"/>
+      <c r="I50" s="4"/>
     </row>
     <row r="51" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="20"/>
+      <c r="A51" s="3"/>
       <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
+      <c r="C51" s="5"/>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
-      <c r="I51" s="21"/>
+      <c r="I51" s="3"/>
     </row>
     <row r="52" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="18"/>
+      <c r="A52" s="4"/>
       <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
+      <c r="C52" s="6"/>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
       <c r="F52" s="4"/>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
-      <c r="I52" s="19"/>
+      <c r="I52" s="4"/>
     </row>
     <row r="53" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="20"/>
+      <c r="A53" s="3"/>
       <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
+      <c r="C53" s="5"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
-      <c r="I53" s="21"/>
+      <c r="I53" s="3"/>
     </row>
     <row r="54" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="18"/>
+      <c r="A54" s="4"/>
       <c r="B54" s="4"/>
-      <c r="C54" s="4"/>
+      <c r="C54" s="6"/>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
       <c r="F54" s="4"/>
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
-      <c r="I54" s="19"/>
+      <c r="I54" s="4"/>
     </row>
     <row r="55" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="20"/>
+      <c r="A55" s="3"/>
       <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
+      <c r="C55" s="5"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
-      <c r="I55" s="21"/>
+      <c r="I55" s="3"/>
     </row>
     <row r="56" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="22"/>
-      <c r="B56" s="23"/>
-      <c r="C56" s="23"/>
-      <c r="D56" s="23"/>
-      <c r="E56" s="23"/>
-      <c r="F56" s="23"/>
-      <c r="G56" s="23"/>
-      <c r="H56" s="23"/>
-      <c r="I56" s="24"/>
+      <c r="A56" s="4"/>
+      <c r="B56" s="4"/>
+      <c r="C56" s="6"/>
+      <c r="D56" s="4"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+      <c r="I56" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1335,15 +1168,15 @@
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="whole" errorTitle="Nivel inválido" error="El nivel debe ser 1 a 5" sqref="D7:D56" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="whole" errorTitle="Nivel inválido" error="El nivel debe ser 1 a 5" sqref="D6:D56" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>1</formula1>
       <formula2>5</formula2>
     </dataValidation>
-    <dataValidation type="whole" errorTitle="Valor inválido" error="Ingresá un número entre 0 y 50" sqref="E7:E56" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="whole" errorTitle="Valor inválido" error="Ingresá un número entre 0 y 50" sqref="E6:E56" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>0</formula1>
       <formula2>50</formula2>
     </dataValidation>
-    <dataValidation type="list" errorTitle="Valor inválido" error="Ingresá SI o NO" sqref="H7:H56" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" errorTitle="Valor inválido" error="Ingresá SI o NO" sqref="H6:H56" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
   </dataValidations>

--- a/VERTEX_Instructores_Modelo.xlsx
+++ b/VERTEX_Instructores_Modelo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agust\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D62F9CB6-51C4-41A9-BBEC-CCD9980CA5CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E87B32F3-B25E-4B16-B99E-ED8EEDBF5662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>VERTEX — Carga masiva de instructores</t>
   </si>
@@ -79,7 +79,22 @@
     <t>DD/MM/AAAA</t>
   </si>
   <si>
+    <t>Inglés</t>
+  </si>
+  <si>
     <t>Inglés, Portugués, Francés, Alemán, Italiano (separar con coma)</t>
+  </si>
+  <si>
+    <t>Agustin Prueba</t>
+  </si>
+  <si>
+    <t>+54 9 221 419-6634</t>
+  </si>
+  <si>
+    <t>Snowboard</t>
+  </si>
+  <si>
+    <t>SI</t>
   </si>
 </sst>
 </file>
@@ -173,7 +188,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -199,6 +214,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -592,7 +610,7 @@
         <v>16</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>17</v>
@@ -602,15 +620,33 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
+      <c r="A6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="4">
+        <v>42776886</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="4">
+        <v>3</v>
+      </c>
+      <c r="E6" s="4">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" s="10">
+        <v>36721</v>
+      </c>
     </row>
     <row r="7" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>

--- a/VERTEX_Instructores_Modelo.xlsx
+++ b/VERTEX_Instructores_Modelo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agust\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E87B32F3-B25E-4B16-B99E-ED8EEDBF5662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24FC308E-6B1D-46D1-84BD-0AF4728DC5F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>VERTEX — Carga masiva de instructores</t>
   </si>
@@ -79,22 +79,7 @@
     <t>DD/MM/AAAA</t>
   </si>
   <si>
-    <t>Inglés</t>
-  </si>
-  <si>
     <t>Inglés, Portugués, Francés, Alemán, Italiano (separar con coma)</t>
-  </si>
-  <si>
-    <t>Agustin Prueba</t>
-  </si>
-  <si>
-    <t>+54 9 221 419-6634</t>
-  </si>
-  <si>
-    <t>Snowboard</t>
-  </si>
-  <si>
-    <t>SI</t>
   </si>
 </sst>
 </file>
@@ -208,15 +193,15 @@
     <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -535,30 +520,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
     </row>
     <row r="2" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
     </row>
     <row r="3" spans="1:9" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -610,7 +595,7 @@
         <v>16</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>17</v>
@@ -620,33 +605,15 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="4">
-        <v>42776886</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="4">
-        <v>3</v>
-      </c>
-      <c r="E6" s="4">
-        <v>1</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I6" s="10">
-        <v>36721</v>
-      </c>
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="7"/>
     </row>
     <row r="7" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>

--- a/VERTEX_Instructores_Modelo.xlsx
+++ b/VERTEX_Instructores_Modelo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agust\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24FC308E-6B1D-46D1-84BD-0AF4728DC5F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{007C8A71-1F54-4587-BA15-E82A7C4FA6BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
